--- a/activities/activity-10-build-a-reconciled-financial-reporting-pack/activity-10-control.xlsx
+++ b/activities/activity-10-build-a-reconciled-financial-reporting-pack/activity-10-control.xlsx
@@ -724,11 +724,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="56311194"/>
-        <c:axId val="33221808"/>
+        <c:axId val="31011820"/>
+        <c:axId val="88600397"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="56311194"/>
+        <c:axId val="31011820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -761,7 +761,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33221808"/>
+        <c:crossAx val="88600397"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -769,7 +769,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33221808"/>
+        <c:axId val="88600397"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -845,7 +845,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56311194"/>
+        <c:crossAx val="31011820"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
